--- a/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/sox_controls.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/11_risk_controls_responsible_ai/sox_controls.xlsx
@@ -484,12 +484,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -545,12 +545,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -655,17 +655,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -748,12 +748,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -787,17 +787,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -831,17 +831,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1315,12 +1315,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1337,17 +1337,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>Treasury</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1457,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1469,17 +1469,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Effective</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1491,12 +1491,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>O2C</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Material weakness candidate</t>
         </is>
       </c>
     </row>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1623,7 +1623,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ITGC</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Non-key</t>
+          <t>Key</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Treasury</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Deficiency</t>
+          <t>Effective</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>P2P</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>O2C</t>
+          <t>R2R</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Key</t>
+          <t>Non-key</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>P2P</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>R2R</t>
+          <t>ITGC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Material weakness candidate</t>
+          <t>Deficiency</t>
         </is>
       </c>
     </row>
